--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1942,6 +1942,165 @@
       </c>
       <c r="AU9" s="3" t="n">
         <v>46202.67708333334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46202.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1883,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>4.46</v>
       </c>
       <c r="R2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2.1</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.46</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>3.25</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.46</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>3.25</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.9</v>
+        <v>4.46</v>
       </c>
       <c r="R3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
         <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -932,10 +932,10 @@
         <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
         <v>1.65</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="AK3" t="n">
         <v>1.17</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,10 +1370,10 @@
         <v>4.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1529,10 +1529,10 @@
         <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,40 +1847,40 @@
         <v>2.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
         <v>1.81</v>
@@ -1889,13 +1889,13 @@
         <v>1.86</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>2.35</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.23</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.05</v>
       </c>
       <c r="R8" t="n">
         <v>2.35</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>4.46</v>
       </c>
       <c r="R2" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.75</v>
       </c>
-      <c r="U2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,71 +893,71 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.46</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.3</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>4.46</v>
@@ -764,7 +764,7 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
         <v>2.1</v>
@@ -779,10 +779,10 @@
         <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.81</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
         <v>1.17</v>
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>1.4</v>
@@ -917,31 +917,31 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
         <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD3" t="n">
         <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB5" t="n">
         <v>1.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD5" t="n">
         <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.23</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>2.35</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.01</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>3.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.46</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>4.01</v>
       </c>
       <c r="O3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.25</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AC3" t="n">
         <v>2.75</v>
       </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>4.01</v>
       </c>
       <c r="O2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.25</v>
       </c>
-      <c r="P2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2.1</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="AC2" t="n">
         <v>2.75</v>
       </c>
-      <c r="U2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.01</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>3.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.46</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="R5" t="n">
         <v>2.06</v>
@@ -1247,7 +1247,7 @@
         <v>1.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AD5" t="n">
         <v>1.27</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
         <v>2.5</v>
@@ -752,25 +752,25 @@
         <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD2" t="n">
         <v>1.38</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK2" t="n">
         <v>1.17</v>
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.75</v>
       </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.23</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>2.35</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,47 +1394,47 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.16</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
         <v>2.35</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
         <v>3.82</v>
@@ -1847,55 +1847,55 @@
         <v>2.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
         <v>1.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK9" t="n">
         <v>1.44</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
         <v>4.2</v>
@@ -2006,43 +2006,43 @@
         <v>5.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="AD10" t="n">
         <v>1.33</v>
@@ -2051,10 +2051,10 @@
         <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.54</v>
+        <v>2.71</v>
       </c>
       <c r="R2" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3.14</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.07</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
         <v>1.74</v>
@@ -1253,7 +1253,7 @@
         <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
         <v>1.76</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="P9" t="n">
         <v>2.27</v>
@@ -1850,19 +1850,19 @@
         <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="S9" t="n">
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W9" t="n">
         <v>1.22</v>
@@ -1886,7 +1886,7 @@
         <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.36</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>5.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
         <v>2.3</v>
@@ -2015,16 +2015,16 @@
         <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
         <v>2.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -2039,16 +2039,16 @@
         <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
         <v>3.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
         <v>2.11</v>
@@ -2070,7 +2070,7 @@
         <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.71</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2.07</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.14</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
         <v>2.35</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>3.83</v>
@@ -1862,7 +1862,7 @@
         <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="W9" t="n">
         <v>1.22</v>
@@ -1886,7 +1886,7 @@
         <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="R2" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3.14</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.07</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>2.35</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.23</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.05</v>
       </c>
       <c r="R7" t="n">
         <v>2.35</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,47 +1553,47 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.16</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
         <v>2.35</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -740,10 +740,10 @@
         <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U2" t="n">
         <v>2.75</v>
@@ -752,7 +752,7 @@
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1.05</v>
@@ -761,7 +761,7 @@
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
         <v>2</v>
@@ -782,7 +782,7 @@
         <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -896,19 +896,19 @@
         <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
@@ -917,31 +917,31 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
         <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>3.95</v>
@@ -1241,19 +1241,19 @@
         <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
         <v>3.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
         <v>1.76</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
         <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
         <v>2.35</v>
@@ -1700,59 +1700,59 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.48</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1856,13 +1856,13 @@
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="W9" t="n">
         <v>1.22</v>
@@ -1871,10 +1871,10 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.33</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
         <v>4.2</v>
@@ -2006,7 +2006,7 @@
         <v>5.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
         <v>2.3</v>
@@ -2015,46 +2015,46 @@
         <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="n">
         <v>2.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>4.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
         <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.48</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="R8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.35</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AD8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.71</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.3</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.3</v>
       </c>
-      <c r="T2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="R6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.35</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AD6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.4</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.1</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1211,68 +1211,68 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.65</v>
       </c>
       <c r="AK5" t="n">
         <v>1.25</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.4</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>3.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
         <v>2.49</v>
@@ -1574,10 +1574,10 @@
         <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2.25</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="P9" t="n">
         <v>2.27</v>
@@ -2006,7 +2006,7 @@
         <v>5.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
         <v>2.3</v>
@@ -2015,16 +2015,16 @@
         <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
         <v>2.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -2033,22 +2033,22 @@
         <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
         <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
         <v>3.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
         <v>2.05</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.27</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>3.2</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.1</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.27</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>3.2</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="P9" t="n">
         <v>2.27</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.27</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>3.2</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.1</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.27</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>3.2</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.27</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>3.2</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.25</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>4.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.47</v>
+        <v>2.06</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1844,25 +1844,25 @@
         <v>3.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
         <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S9" t="n">
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W9" t="n">
         <v>1.22</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>4.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1942,165 +1942,6 @@
       </c>
       <c r="AU9" s="3" t="n">
         <v>46202.67708333334</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>46202</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
-        <v>46202.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.1</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.27</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>3.2</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>4.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.27</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.92</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
         <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
@@ -1232,16 +1232,16 @@
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
         <v>1.72</v>
@@ -1256,7 +1256,7 @@
         <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
         <v>1.93</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AK5" t="n">
         <v>1.25</v>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="P6" t="n">
-        <v>4.34</v>
+        <v>4.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
         <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1394,31 +1394,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
         <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.14</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P9" t="n">
         <v>2.22</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.45</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="R2" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3.25</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.05</v>
+        <v>4.45</v>
       </c>
       <c r="O3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.25</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.64</v>
+        <v>1.12</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.58</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>4.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>4.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>2.07</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
         <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.07</v>
+        <v>2.86</v>
       </c>
       <c r="R8" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
         <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P9" t="n">
         <v>2.22</v>
@@ -1856,7 +1856,7 @@
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
@@ -1892,7 +1892,7 @@
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.05</v>
+        <v>4.45</v>
       </c>
       <c r="O2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.25</v>
       </c>
-      <c r="P2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.1</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.64</v>
+        <v>1.12</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.45</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.25</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
         <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.07</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
         <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>4.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.86</v>
+        <v>2.07</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
         <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.45</v>
+        <v>6.25</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,28 +884,28 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
         <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
@@ -923,7 +923,7 @@
         <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
         <v>1.75</v>
@@ -941,7 +941,7 @@
         <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
         <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
         <v>1.38</v>
@@ -1229,7 +1229,7 @@
         <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.06</v>
@@ -1244,7 +1244,7 @@
         <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
         <v>3.28</v>
@@ -1253,10 +1253,10 @@
         <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG5" t="n">
         <v>1.67</v>
@@ -1275,7 +1275,7 @@
         <v>1.84</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.49</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.13</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
         <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
@@ -1718,25 +1718,25 @@
         <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
         <v>2.22</v>
@@ -1856,7 +1856,7 @@
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
@@ -1911,7 +1911,7 @@
         <v>1.62</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>6.25</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="R2" t="n">
-        <v>2.49</v>
+        <v>1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T2" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
         <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>6.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>2.49</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.91</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
         <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.53</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>4.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="V6" t="n">
         <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK6" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.75</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="V8" t="n">
         <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.54</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
         <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1394,31 +1394,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD6" t="n">
         <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>1.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S7" t="n">
         <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.09</v>
@@ -1553,31 +1553,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
         <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="S2" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.91</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF2" t="n">
         <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6.25</v>
+        <v>2.01</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.49</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.22</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
         <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>3.3</v>
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
         <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG5" t="n">
         <v>1.67</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.84</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.35</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V6" t="n">
         <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
         <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.54</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
         <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.04</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,34 +1838,34 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
         <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="S9" t="n">
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1892,7 +1892,7 @@
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK9" t="n">
         <v>1.44</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '45+3']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46202.5</v>
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '84']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46202.5</v>
@@ -1020,26 +1020,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '47', '62']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46202.52083333334</v>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1194,11 +1194,11 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '90+8']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46202.53125</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
         <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.1</v>
@@ -1394,31 +1394,31 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
         <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>3.36</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
         <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.16</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -693,28 +693,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -725,107 +725,107 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>6.3</v>
+        <v>2.01</v>
       </c>
       <c r="O2" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.22</v>
       </c>
-      <c r="T2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
         <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>['45', '84']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>['11', '45+3']</t>
-        </is>
-      </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
         <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.63</v>
+        <v>1.16</v>
       </c>
       <c r="AS2" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="AT2" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46202.5</v>
@@ -852,28 +852,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -884,107 +884,107 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>6.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.03</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
         <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['45', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '45+3']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.16</v>
+        <v>1.63</v>
       </c>
       <c r="AS3" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="AT3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46202.5</v>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1357,35 +1357,35 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
         <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
         <v>1.1</v>
@@ -1394,31 +1394,31 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
         <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1427,41 +1427,41 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46202.60416666666</v>
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '31', '45+1']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '53', '75']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46202.60416666666</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.36</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AD8" t="n">
         <v>1.44</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['34', '41', '71', '90+2']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46202.60416666666</v>
@@ -1818,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1834,38 +1834,38 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
         <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="S9" t="n">
         <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1892,7 +1892,7 @@
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
@@ -1904,41 +1904,41 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '23']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
         <v>1.57</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46202.67708333334</v>

--- a/jogos_2026-06-29.xlsx
+++ b/jogos_2026-06-29.xlsx
@@ -1329,63 +1329,63 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
         <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.1</v>
@@ -1394,74 +1394,74 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
         <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '41', '71', '90+2']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AN6" t="n">
         <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.93</v>
+        <v>2.29</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="AT6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46202.60416666666</v>
@@ -1488,22 +1488,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['8', '31', '45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['41', '53', '75']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
         <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
         <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.96</v>
+        <v>0.93</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="AS7" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="AT7" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46202.60416666666</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>3.36</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
         <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>['34', '41', '71', '90+2']</t>
+          <t>['8', '31', '45+1']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['41', '53', '75']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.16</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
         <v>3</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AT8" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46202.60416666666</v>
